--- a/Results/Study 1/ResNet18 (pretrained)/Confusion Matrices.xlsx
+++ b/Results/Study 1/ResNet18 (pretrained)/Confusion Matrices.xlsx
@@ -400,10 +400,10 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>541</v>
+        <v>445</v>
       </c>
       <c r="C2">
-        <v>99</v>
+        <v>195</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -411,10 +411,10 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>351</v>
+        <v>137</v>
       </c>
       <c r="C3">
-        <v>289</v>
+        <v>503</v>
       </c>
     </row>
   </sheetData>
@@ -440,10 +440,10 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>141</v>
+        <v>95</v>
       </c>
       <c r="C2">
-        <v>19</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -451,10 +451,10 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>99</v>
+        <v>28</v>
       </c>
       <c r="C3">
-        <v>61</v>
+        <v>132</v>
       </c>
     </row>
   </sheetData>
